--- a/output/roomself_excel/14405.xlsx
+++ b/output/roomself_excel/14405.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>101016</v>
+        <v>142631</v>
       </c>
       <c r="D2" t="n">
-        <v>2632</v>
+        <v>3084</v>
       </c>
       <c r="E2" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169624</v>
+        <v>123122</v>
       </c>
       <c r="D3" t="n">
-        <v>4656</v>
+        <v>2880</v>
       </c>
       <c r="E3" t="n">
-        <v>815</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89940</v>
+        <v>101016</v>
       </c>
       <c r="D4" t="n">
-        <v>2612</v>
+        <v>2632</v>
       </c>
       <c r="E4" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19152</v>
+        <v>89940</v>
       </c>
       <c r="D5" t="n">
-        <v>1108</v>
+        <v>2612</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>401</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>142631</v>
+        <v>31493</v>
       </c>
       <c r="D6" t="n">
-        <v>3084</v>
+        <v>1496</v>
       </c>
       <c r="E6" t="n">
-        <v>450</v>
+        <v>217</v>
       </c>
       <c r="F6" t="n">
-        <v>356</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31493</v>
+        <v>46502</v>
       </c>
       <c r="D7" t="n">
-        <v>1496</v>
+        <v>2120</v>
       </c>
       <c r="E7" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1056</v>
+        <v>5084</v>
       </c>
       <c r="D8" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5084</v>
+        <v>19152</v>
       </c>
       <c r="D9" t="n">
-        <v>600</v>
+        <v>1108</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,38 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D10" t="n">
+        <v>280</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>1365</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>296</v>
       </c>
-      <c r="E10" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" t="n">
-        <v>34</v>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14405.xlsx
+++ b/output/roomself_excel/14405.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
         </is>
       </c>
     </row>
@@ -475,12 +480,9 @@
       <c r="D2" t="n">
         <v>3084</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +499,9 @@
       <c r="D3" t="n">
         <v>2880</v>
       </c>
-      <c r="E3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +518,9 @@
       <c r="D4" t="n">
         <v>2632</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +537,16 @@
       <c r="D5" t="n">
         <v>2612</v>
       </c>
-      <c r="E5" t="n">
-        <v>401</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>247</v>
+        <v>372</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +564,15 @@
       <c r="D6" t="n">
         <v>1496</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>217</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -585,12 +591,9 @@
       <c r="D7" t="n">
         <v>2120</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,10 +610,15 @@
       <c r="D8" t="n">
         <v>600</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>74</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>25</v>
       </c>
     </row>
@@ -629,10 +637,15 @@
       <c r="D9" t="n">
         <v>1108</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>133</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>23</v>
       </c>
     </row>
@@ -651,12 +664,9 @@
       <c r="D10" t="n">
         <v>280</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +683,9 @@
       <c r="D11" t="n">
         <v>296</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/14405.xlsx
+++ b/output/roomself_excel/14405.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,26 @@
           <t>ExtWallWidth_1</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -483,6 +503,10 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -502,6 +526,10 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -521,6 +549,10 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -548,6 +580,10 @@
       <c r="G5" t="n">
         <v>14</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -575,6 +611,10 @@
       <c r="G6" t="n">
         <v>14</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -594,6 +634,10 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -621,6 +665,22 @@
       <c r="G8" t="n">
         <v>25</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>66</v>
+      </c>
+      <c r="K8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -648,6 +708,10 @@
       <c r="G9" t="n">
         <v>23</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -667,6 +731,10 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -686,6 +754,10 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
